--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,8 +537,14 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -568,7 +574,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
@@ -578,8 +584,14 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -609,7 +621,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
@@ -619,8 +631,14 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,7 +668,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
@@ -660,8 +678,14 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,7 +715,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
@@ -701,8 +725,14 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -746,8 +776,14 @@
           <t>token</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -777,7 +813,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
@@ -787,8 +823,14 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>-400</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -818,7 +860,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
@@ -828,8 +870,14 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>-400</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -855,11 +903,11 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{"goods_id":"99999"}</t>
+          <t>{"goods_id":"99999","stock":1}</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>404</v>
+        <v>200</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
@@ -873,8 +921,14 @@
           <t>token</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -900,11 +954,11 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{"goods_id":""}</t>
+          <t>{"goods_id":"","stock":1}</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
@@ -918,8 +972,14 @@
           <t>token</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -963,8 +1023,14 @@
           <t>token</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -994,7 +1060,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
@@ -1004,8 +1070,14 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>-400</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1035,7 +1107,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
@@ -1045,8 +1117,14 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>-400</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1072,16 +1150,16 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{"id":"99999"}</t>
+          <t>{"id":""}</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>404</v>
+        <v>200</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>收藏-不存在的商品ID</t>
+          <t>收藏-空商品ID</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1090,98 +1168,14 @@
           <t>token</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>hc_shop_api_205</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>http://shop-xo.hctestedu.com/index.php?s=api/goods/favor&amp;token=$token</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>{"application":"app","application_client_type":"weixin"}</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>{"id":""}</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>400</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>收藏-空商品ID</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>token</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>hc_shop_api_206</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>http://shop-xo.hctestedu.com/index.php?s=api/goods/favor&amp;token=$token</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>{"application":"app","application_client_type":"weixin"}</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>{"id":"2"}</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>200</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>收藏-重复收藏同一商品</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>token</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>-1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
